--- a/CBT_2021_2회/산업안전기사_2021_2회_문항등록.xlsx
+++ b/CBT_2021_2회/산업안전기사_2021_2회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="AI11" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;리더십 이론&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「특성 · 행동 · 상황」 순으로 발전&lt;/strong&gt; 했다 — &lt;strong&gt;타고난 자질을 찾다가(특성), 행동을 보다가(행동), 결국 때와 곳에 달렸다(상황)&lt;/strong&gt;로 옮겨 갔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;리더의 자질을 보면 특성이론&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;리더십 이론&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「특성 · 행동 · 상황」 순으로 발전&lt;/strong&gt;했다 — &lt;strong&gt;타고난 자질을 찾다가(특성), 행동을 보다가(행동), 결국 때와 곳에 달렸다(상황)&lt;/strong&gt;로 옮겨 갔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;리더의 자질을 보면 특성이론&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2616,17 +2616,17 @@
       </c>
       <c r="AG12" s="32" t="inlineStr">
         <is>
-          <t>TWI 는 &lt;strong&gt;JIT · JMT · JRT · JST&lt;/strong&gt; 넷이다. &lt;strong&gt;「문제해결훈련」은 들지 않는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;TWI 의 네 과정&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;약칭&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JIT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업지도훈련(Job Instruction Training)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가르치는 법&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JMT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업방법훈련(Job Method Training)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;개선하는 법&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JRT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인간관계훈련(Job Relations Training)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사람 다루는 법&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JST&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업안전훈련(Job Safety Training)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전하게 하는 법&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;문제해결훈련&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;TWI 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>TWI는 &lt;strong&gt;JIT · JMT · JRT · JST&lt;/strong&gt; 넷이다. &lt;strong&gt;「문제해결훈련」은 들지 않는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;TWI의 네 과정&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;약칭&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JIT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업지도훈련(Job Instruction Training)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가르치는 법&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JMT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업방법훈련(Job Method Training)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;개선하는 법&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JRT&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인간관계훈련(Job Relations Training)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사람 다루는 법&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JST&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업안전훈련(Job Safety Training)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전하게 하는 법&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;문제해결훈련&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;TWI가 아니다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH12" s="32" t="inlineStr">
         <is>
-          <t>② 작업지도훈련은 TWI 의 하나다.&lt;br&gt;③ 인간관계훈련도 그렇다.&lt;br&gt;④ 작업방법훈련도 그렇다.</t>
+          <t>② 작업지도훈련은 TWI의 하나다.&lt;br&gt;③ 인간관계훈련도 그렇다.&lt;br&gt;④ 작업방법훈련도 그렇다.</t>
         </is>
       </c>
       <c r="AI12" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;TWI(Training Within Industry)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;넷 모두 「작업」이나 「인간관계」로 현장의 일&lt;/strong&gt;을 가리킨다 — &lt;strong&gt;「문제해결」은 두루뭉술해 TWI 의 이름과 결이 다르다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;TWI 는 지도·방법·관계·안전 넷&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;TWI(Training Within Industry)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;넷 모두 「작업」이나 「인간관계」로 현장의 일&lt;/strong&gt;을 가리킨다 — &lt;strong&gt;「문제해결」은 두루뭉술해 TWI의 이름과 결이 다르다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;TWI는 지도·방법·관계·안전 넷&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2874,17 +2874,17 @@
       </c>
       <c r="AG14" s="32" t="inlineStr">
         <is>
-          <t>하인리히는 &lt;strong&gt;1 : 29 : 300&lt;/strong&gt;이다. &lt;strong&gt;경상해 58 = 29 × 2&lt;/strong&gt;이므로 &lt;strong&gt;모두 2배&lt;/strong&gt; 해 &lt;strong&gt;2 : 58 : 600&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해구성비율&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이론&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비율&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하인리히&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 29 : 300&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중상 : 경상 : 무상해&lt;/u&gt; · 합계 330&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버드&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 10 : 30 : 600&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;중상 : 경상 : 물적손해 : 무상해무손실&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;58 ÷ 29 = 2 배 → 2 : 58 : 600&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>하인리히는 &lt;strong&gt;1 : 29 : 300&lt;/strong&gt;이다. &lt;strong&gt;경상해 58 = 29 × 2&lt;/strong&gt;이므로 &lt;strong&gt;모두 2배&lt;/strong&gt;해 &lt;strong&gt;2 : 58 : 600&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해구성비율&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이론&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비율&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하인리히&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 29 : 300&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중상 : 경상 : 무상해&lt;/u&gt; · 합계 330&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버드&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 : 10 : 30 : 600&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;중상 : 경상 : 물적손해 : 무상해무손실&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;58 ÷ 29 = 2 배 → 2 : 58 : 600&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH14" s="32" t="inlineStr">
         <is>
-          <t>② 3 : 58 : 660 은 배수가 맞지 않는다.&lt;br&gt;③ 6 : 58 : 330 은 하인리히 비율과 어긋난다.&lt;br&gt;④ 10 : 58 : 600 도 그렇다.</t>
+          <t>② 3 : 58 : 660은 배수가 맞지 않는다.&lt;br&gt;③ 6 : 58 : 330은 하인리히 비율과 어긋난다.&lt;br&gt;④ 10 : 58 : 600 도 그렇다.</t>
         </is>
       </c>
       <c r="AI14" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;하인리히의 재해구성비율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;가운데 수 29 를 기준으로 배수를 잡는다&lt;/strong&gt; — &lt;strong&gt;58 은 29 의 두 배&lt;/strong&gt; 이니 앞뒤도 두 배다. &lt;strong&gt;330 이라는 합계 숫자에 끌리면 ③을 고르게&lt;/strong&gt; 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하인리히 1 : 29 : 300&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;하인리히의 재해구성비율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;가운데 수 29를 기준으로 배수를 잡는다&lt;/strong&gt; — &lt;strong&gt;58은 29의 두 배&lt;/strong&gt; 이니 앞뒤도 두 배다. &lt;strong&gt;330이라는 합계 숫자에 끌리면 ③을 고르게&lt;/strong&gt; 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;하인리히 1 : 29 : 300&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AI15" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;버즈 세션&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「버즈(buzz)」는 벌이 윙윙거리는 소리&lt;/strong&gt;다 — &lt;strong&gt;여러 소집단이 한꺼번에 떠드는 소리&lt;/strong&gt;에서 온 이름이다. &lt;strong&gt;6-6 이라는 숫자가 곧 6명 6분&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;6-6 회의는 버즈 세션&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;버즈 세션&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「버즈(buzz)」는 벌이 윙윙거리는 소리&lt;/strong&gt;다 — &lt;strong&gt;여러 소집단이 한꺼번에 떠드는 소리&lt;/strong&gt;에서 온 이름이다. &lt;strong&gt;6-6이라는 숫자가 곧 6명 6분&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;6-6 회의는 버즈 세션&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3657,12 +3657,12 @@
       </c>
       <c r="AH20" s="32" t="inlineStr">
         <is>
-          <t>① 480 은 근로시간을 절반으로 잡은 값이다.&lt;br&gt;② 720 은 계산과 맞지 않는다.&lt;br&gt;④ 1440 도 그렇다.</t>
+          <t>① 480은 근로시간을 절반으로 잡은 값이다.&lt;br&gt;② 720은 계산과 맞지 않는다.&lt;br&gt;④ 1440 도 그렇다.</t>
         </is>
       </c>
       <c r="AI20" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;강도율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;강도율은 「1,000시간당 며칠을 잃었나」&lt;/strong&gt;다 — &lt;strong&gt;총 근로시간 240만 시간은 1,000시간짜리가 2,400묶음&lt;/strong&gt; 이니 0.4 × 2,400 = 960 으로 곧장 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;근로손실일수 = 강도율 × 연근로시간 ÷ 1,000&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;강도율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;강도율은 「1,000시간당 며칠을 잃었나」&lt;/strong&gt;다 — &lt;strong&gt;총 근로시간 240만 시간은 1,000시간짜리가 2,400묶음&lt;/strong&gt; 이니 0.4 × 2,400 = 960으로 곧장 나온다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;근로손실일수 = 강도율 × 연근로시간 ÷ 1,000&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="AG22" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;신체장해등급 4 ~ 14급&lt;/strong&gt;은 &lt;strong&gt;영구 일부노동불능&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;ILO 의 산업재해 정도구분&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사망&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;근로손실일수 7,500일&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;영구 전노동불능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;신체장해등급 1 ~ 3급&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;7,500일&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;영구 일부노동불능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;신체장해등급 4 ~ 14급&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항 — 12급&lt;/u&gt; · 등급별 일수&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일시 전노동불능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;의사의 진단으로 일정 기간 노동을 못 한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일시 일부노동불능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가벼운 작업만 가능&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;신체장해등급 4 ~ 14급&lt;/strong&gt;은 &lt;strong&gt;영구 일부노동불능&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;ILO의 산업재해 정도구분&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사망&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;근로손실일수 7,500일&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;영구 전노동불능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;신체장해등급 1 ~ 3급&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;7,500일&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;영구 일부노동불능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;신체장해등급 4 ~ 14급&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항 — 12급&lt;/u&gt; · 등급별 일수&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일시 전노동불능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;의사의 진단으로 일정 기간 노동을 못 한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일시 일부노동불능&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;가벼운 작업만 가능&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH22" s="32" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AI22" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;ILO 의 재해 정도구분&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「영구」인가 「일시」인가는 장해가 남았는가&lt;/strong&gt;로, &lt;strong&gt;「전」인가 「일부」인가는 1 ~ 3급인가 4 ~ 14급인가&lt;/strong&gt;로 갈린다. &lt;strong&gt;12급은 장해가 남았으니 영구, 3급을 넘으니 일부&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1 ~ 3급은 영구 전노동불능, 4 ~ 14급은 영구 일부노동불능&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;ILO의 재해 정도구분&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「영구」인가 「일시」인가는 장해가 남았는가&lt;/strong&gt;로, &lt;strong&gt;「전」인가 「일부」인가는 1 ~ 3급인가 4 ~ 14급인가&lt;/strong&gt;로 갈린다. &lt;strong&gt;12급은 장해가 남았으니 영구, 3급을 넘으니 일부&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1 ~ 3급은 영구 전노동불능, 4 ~ 14급은 영구 일부노동불능&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AG23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;조합 AND 게이트&lt;/strong&gt;다. &lt;strong&gt;「n개 중 k개가 일어나면」&lt;/strong&gt;이라는 조건이 붙는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 의 수정게이트&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조합 AND 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여러 입력 가운데 정해진 개수가 일어나면 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · 3개 중 2개&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;우선적 AND 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 정해진 순서로 일어날 때만 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배타적 OR 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력 가운데 하나만 일어날 때 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;둘 이상이면 출력 없음&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험지속기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 일정 시간 이어져야 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;억제 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조건이 만족될 때만 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;수정기호 안에 조건을 적는다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;조합 AND 게이트&lt;/strong&gt;다. &lt;strong&gt;「n개 중 k개가 일어나면」&lt;/strong&gt;이라는 조건이 붙는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA의 수정게이트&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;조건&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;조합 AND 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여러 입력 가운데 정해진 개수가 일어나면 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · 3개 중 2개&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;우선적 AND 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 정해진 순서로 일어날 때만 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배타적 OR 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력 가운데 하나만 일어날 때 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;둘 이상이면 출력 없음&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험지속기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입력이 일정 시간 이어져야 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;억제 게이트&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조건이 만족될 때만 출력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;수정기호 안에 조건을 적는다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH23" s="32" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="AI23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 수정게이트&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「개수」면 조합, 「순서」면 우선적, 「시간」이면 위험지속, 「하나만」이면 배타적&lt;/strong&gt;이다 — &lt;strong&gt;네 조건이 하나씩&lt;/strong&gt; 걸려 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;3개 중 2개면 조합 AND 게이트&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 수정게이트&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「개수」면 조합, 「순서」면 우선적, 「시간」이면 위험지속, 「하나만」이면 배타적&lt;/strong&gt;이다 — &lt;strong&gt;네 조건이 하나씩&lt;/strong&gt; 걸려 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;3개 중 2개면 조합 AND 게이트&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AG24" s="32" t="inlineStr">
         <is>
-          <t>왼쪽 &lt;strong&gt;집 모양(오각형)은 통상사상&lt;/strong&gt;, 오른쪽 &lt;strong&gt;마름모는 생략사상&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 의 사상기호&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직사각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;결함사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;정상사상과 중간사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기본사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;더 나눌 수 없는 밑바닥 사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;집 모양(오각형)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;통상사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;통상 발생이 예상되는 사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;마름모&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생략사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;정보가 부족해 더 나누지 않은 사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;삼각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전이기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다른 곳으로 이어진다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>왼쪽 &lt;strong&gt;집 모양(오각형)은 통상사상&lt;/strong&gt;, 오른쪽 &lt;strong&gt;마름모는 생략사상&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA의 사상기호&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직사각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;결함사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;정상사상과 중간사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기본사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;더 나눌 수 없는 밑바닥 사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;집 모양(오각형)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;통상사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;통상 발생이 예상되는 사상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;마름모&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생략사상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;정보가 부족해 더 나누지 않은 사상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;삼각형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전이기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다른 곳으로 이어진다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH24" s="32" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AI24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 사상기호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「집은 늘 있으니 통상사상, 마름모는 생략」&lt;/strong&gt;으로 묶는다 — &lt;strong&gt;삼각형만 전이기호&lt;/strong&gt;라 세 모양이 겹치지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;집 모양은 통상사상, 마름모는 생략사상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 사상기호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「집은 늘 있으니 통상사상, 마름모는 생략」&lt;/strong&gt;으로 묶는다 — &lt;strong&gt;삼각형만 전이기호&lt;/strong&gt;라 세 모양이 겹치지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;집 모양은 통상사상, 마름모는 생략사상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4551,17 +4551,17 @@
       </c>
       <c r="AG27" s="32" t="inlineStr">
         <is>
-          <t>$A \cdot \bar{A} = 0$이다. &lt;strong&gt;A 와 A 아님은 동시에 참일 수 없다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;불 대수의 기본 정리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;정리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$A \cdot 0 = 0$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;무엇과 곱해도 0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$A \cdot 1 = A$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$A + 1 = 1$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;무엇을 더해도 1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$A + 0 = A$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$A \cdot \bar{A} = 0$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상보의 법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「1」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$A + \bar{A} = 1$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$A ( A + B ) = A$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;흡수법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$A \cdot \bar{A} = 0$이다. &lt;strong&gt;A와 A 아님은 동시에 참일 수 없다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;불 대수의 기본 정리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;정리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$A \cdot 0 = 0$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;무엇과 곱해도 0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$A \cdot 1 = A$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$A + 1 = 1$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;무엇을 더해도 1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$A + 0 = A$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$A \cdot \bar{A} = 0$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상보의 법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「1」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$A + \bar{A} = 1$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$A ( A + B ) = A$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;흡수법칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH27" s="32" t="inlineStr">
         <is>
-          <t>① A · 0 = 0 은 옳다.&lt;br&gt;② A + 1 = 1 도 옳다.&lt;br&gt;④ A(A + B) = A 는 흡수법칙으로 옳다.</t>
+          <t>① A · 0 = 0은 옳다.&lt;br&gt;② A + 1 = 1 도 옳다.&lt;br&gt;④ A(A + B) = A는 흡수법칙으로 옳다.</t>
         </is>
       </c>
       <c r="AI27" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;불 대수의 정리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;곱(AND)은 「둘 다 참이라야」&lt;/strong&gt; 이니 &lt;strong&gt;A 와 A 아님을 곱하면 0&lt;/strong&gt;이다 — &lt;strong&gt;합(OR)이라야 1&lt;/strong&gt;이 된다. &lt;strong&gt;「·」과 「+」를 바꿔 놓은 함정&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;A · Ā = 0, A + Ā = 1&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;불 대수의 정리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;곱(AND)은 「둘 다 참이라야」&lt;/strong&gt; 이니 &lt;strong&gt;A와 A 아님을 곱하면 0&lt;/strong&gt;이다 — &lt;strong&gt;합(OR)이라야 1&lt;/strong&gt;이 된다. &lt;strong&gt;「·」과 「+」를 바꿔 놓은 함정&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;A · Ā = 0, A + Ā = 1&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="AI29" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;좌식작업과 입식작업&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;앉으면 몸이 안정되지만 움직임과 힘이 제한&lt;/strong&gt; 된다 — &lt;strong&gt;「정밀 · 가벼움 · 한자리」면 앉고 「힘 · 이동 · 넓은 범위」면 선다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;정밀 조립은 좌식작업&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;좌식작업과 입식작업&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;앉으면 몸이 안정되지만 움직임과 힘이 제한&lt;/strong&gt;된다 — &lt;strong&gt;「정밀 · 가벼움 · 한자리」면 앉고 「힘 · 이동 · 넓은 범위」면 선다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;정밀 조립은 좌식작업&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5059,17 +5059,17 @@
       </c>
       <c r="AG31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;Part of&lt;/strong&gt;다. &lt;strong&gt;「일부만」&lt;/strong&gt;이라는 뜻으로 성질상의 감소를 가리킨다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;HAZOP 의 가이드워드&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가이드워드&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;No / Not&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계 의도가 전혀 이루어지지 않았다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;완전한 부정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;More / Less&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;양적인 증가 또는 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;As well as&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;성질상의 증가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;의도한 것 말고 딴 것도 함께&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Part of&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;성질상의 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일부만 이루어졌다&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Reverse&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계 의도와 반대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Other than&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;완전히 다른 것으로 바뀌었다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;Part of&lt;/strong&gt;다. &lt;strong&gt;「일부만」&lt;/strong&gt;이라는 뜻으로 성질상의 감소를 가리킨다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;HAZOP의 가이드워드&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가이드워드&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;No / Not&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계 의도가 전혀 이루어지지 않았다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;완전한 부정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;More / Less&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;양적인 증가 또는 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;As well as&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;성질상의 증가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;의도한 것 말고 딴 것도 함께&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Part of&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;성질상의 감소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일부만 이루어졌다&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Reverse&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계 의도와 반대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Other than&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;완전히 다른 것으로 바뀌었다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH31" s="32" t="inlineStr">
         <is>
-          <t>② More/Less 는 양적인 증가·감소다.&lt;br&gt;③ No/Not 은 완전한 부정이다.&lt;br&gt;④ Other than 은 완전한 대체다.</t>
+          <t>② More/Less는 양적인 증가·감소다.&lt;br&gt;③ No/Not은 완전한 부정이다.&lt;br&gt;④ Other than은 완전한 대체다.</t>
         </is>
       </c>
       <c r="AI31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;HAZOP 의 가이드워드&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「양」이면 More/Less, 「성질」이면 As well as / Part of&lt;/strong&gt;로 짝을 이룬다 — &lt;strong&gt;성질이 늘면 As well as, 줄면 Part of&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;성질상의 감소는 Part of&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;HAZOP의 가이드워드&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「양」이면 More/Less, 「성질」이면 As well as / Part of&lt;/strong&gt;로 짝을 이룬다 — &lt;strong&gt;성질이 늘면 As well as, 줄면 Part of&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;성질상의 감소는 Part of&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5321,12 +5321,12 @@
       </c>
       <c r="AG33" s="32" t="inlineStr">
         <is>
-          <t>A∥C 와 B∥D 두 병렬 묶음이 &lt;strong&gt;직렬&lt;/strong&gt;로 이어져 있다.$R_{(\text{병렬})} = 1 - ( 1 - r )^{2} = 2 r - r^{2} = r ( 2 - r )$$R = {r ( 2 - r )}^{2} = r^{2} ( 2 - r )^{2}$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;병렬과 직렬의 조합&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;A ∥ C&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$1 - ( 1 - r )^{2} = r ( 2 - r )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B ∥ D&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$r ( 2 - r )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직렬로 이음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;${r ( 2 - r )}^{2} = r^{2} ( 2 - r )^{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;검산 (r = 0.9)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.99² = 0.9801&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;한 개짜리보다 높다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>A∥C와 B∥D 두 병렬 묶음이 &lt;strong&gt;직렬&lt;/strong&gt;로 이어져 있다.$R_{(\text{병렬})} = 1 - ( 1 - r )^{2} = 2 r - r^{2} = r ( 2 - r )$$R = {r ( 2 - r )}^{2} = r^{2} ( 2 - r )^{2}$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;병렬과 직렬의 조합&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;A ∥ C&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$1 - ( 1 - r )^{2} = r ( 2 - r )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B ∥ D&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$r ( 2 - r )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직렬로 이음&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;${r ( 2 - r )}^{2} = r^{2} ( 2 - r )^{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;검산 (r = 0.9)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.99² = 0.9801&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;한 개짜리보다 높다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH33" s="32" t="inlineStr">
         <is>
-          <t>① r(2−r²) 은 묶음이 하나뿐일 때의 꼴이다.&lt;br&gt;③ r²(2−r²) 은 병렬 계산을 잘못한 것이다.&lt;br&gt;④ r²(2−r) 은 제곱을 빠뜨린 것이다.</t>
+          <t>① r(2−r²)은 묶음이 하나뿐일 때의 꼴이다.&lt;br&gt;③ r²(2−r²)은 병렬 계산을 잘못한 것이다.&lt;br&gt;④ r²(2−r)은 제곱을 빠뜨린 것이다.</t>
         </is>
       </c>
       <c r="AI33" s="32" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AG38" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;맥박수와 산소 소비량&lt;/strong&gt;이다. &lt;strong&gt;몸을 심하게 쓰면 심장과 숨이 먼저 반응&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;작업부담의 생리적 척도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;작업의 종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;척도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;육체적(동적) 작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;맥박수 · 산소 소비량 · 심박출량 · 에너지 소비량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정적 근력작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근전도(EMG) · 심박수 · 산소 소비량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정신적 작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;점멸융합주파수(CFF) · 뇌전도(EEG) · 부정맥 지수 · 눈 깜빡임&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생리적 척도가 아니다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;일의 양 자체&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;맥박수와 산소 소비량&lt;/strong&gt;이다. &lt;strong&gt;몸을 심하게 쓰면 심장과 숨이 먼저 반응&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;작업부담의 생리적 척도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;작업의 종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;척도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;육체적(동적) 작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;맥박수 · 산소 소비량 · 심박출량 · 에너지 소비량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정적 근력작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근전도(EMG) · 심박수 · 산소 소비량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정신적 작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;점멸융합주파수(CFF) · 뇌전도(EEG) · 부정맥 지수 · 눈 깜빡임&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;생리적 척도가 아니다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;일의 양 자체&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH38" s="32" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="AG41" s="32" t="inlineStr">
         <is>
-          <t>2단계는 &lt;strong&gt;정성적 평가&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전성 평가의 6단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관계자료의 작성준비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · 입지·배치·건조물·공정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물 · 용 · 온 · 압 · 조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설비·관리 대책&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해정보에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FTA 에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>2단계는 &lt;strong&gt;정성적 평가&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전성 평가의 6단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이름&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관계자료의 작성준비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · 입지·배치·건조물·공정&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물 · 용 · 온 · 압 · 조&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설비·관리 대책&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해정보에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FTA에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH41" s="32" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="AH42" s="32" t="inlineStr">
         <is>
-          <t>② (X1, X3) 은 A₁ 의 X₂ 가 빠져 있다.&lt;br&gt;③ (X2, X3) 은 X₁ 이 빠져 있다.&lt;br&gt;④ (X1, X2, X3) 은 더 줄일 수 있으므로 최소 컷셋이 아니다.</t>
+          <t>② (X1, X3)은 A₁ 의 X₂ 가 빠져 있다.&lt;br&gt;③ (X2, X3)은 X₁ 이 빠져 있다.&lt;br&gt;④ (X1, X2, X3)은 더 줄일 수 있으므로 최소 컷셋이 아니다.</t>
         </is>
       </c>
       <c r="AI42" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;최소 컷셋의 계산&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;AND 는 곱, OR 는 합&lt;/strong&gt;으로 놓고 전개한 뒤 &lt;strong&gt;더 큰 항이 작은 항을 품으면 큰 쪽을 지운다&lt;/strong&gt;. &lt;strong&gt;같은 기호를 여러 번 곱해도 하나(X·X = X)&lt;/strong&gt;라는 것을 잊지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;AND 는 곱, OR 는 합, 포함되는 항은 지운다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;최소 컷셋의 계산&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;AND는 곱, OR는 합&lt;/strong&gt;으로 놓고 전개한 뒤 &lt;strong&gt;더 큰 항이 작은 항을 품으면 큰 쪽을 지운다&lt;/strong&gt;. &lt;strong&gt;같은 기호를 여러 번 곱해도 하나(X·X = X)&lt;/strong&gt;라는 것을 잊지 않는다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;AND는 곱, OR는 합, 포함되는 항은 지운다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6744,17 +6744,17 @@
       </c>
       <c r="AG44" s="32" t="inlineStr">
         <is>
-          <t>$$V = \text{원주길이} \times N = 0.214 \, m \times 500 = 107 \, m / \mathrm{min}$$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;원주속도의 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름으로 구할 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = \dfrac{\pi D N}{1 {,} 000} \, [ m / \mathrm{min} ]$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;D 는 mm&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원주길이가 주어질 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = L \times N$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;L 은 m 로 고쳐서&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.214 × 500 = 107&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$$V = \text{원주길이} \times N = 0.214 \, m \times 500 = 107 \, m / \mathrm{min}$$&lt;div style="margin:12px 0 2px;font-weight:700"&gt;원주속도의 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름으로 구할 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = \dfrac{\pi D N}{1 {,} 000} \, [ m / \mathrm{min} ]$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;D는 mm&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원주길이가 주어질 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = L \times N$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;L은 m로 고쳐서&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.214 × 500 = 107&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH44" s="32" t="inlineStr">
         <is>
-          <t>① 54 는 절반으로 잡은 값이다.&lt;br&gt;③ 214 는 원주길이의 수를 그대로 쓴 값이다.&lt;br&gt;④ 321 은 계산과 맞지 않는다.</t>
+          <t>① 54는 절반으로 잡은 값이다.&lt;br&gt;③ 214는 원주길이의 수를 그대로 쓴 값이다.&lt;br&gt;④ 321은 계산과 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI44" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;연삭기의 원주속도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;원주길이가 이미 주어졌으니 πD 를 다시 구할 것이 없다&lt;/strong&gt; — &lt;strong&gt;mm 를 m 로 바꾸는 것&lt;/strong&gt;만 잊지 않으면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;원주속도 = 원주길이(m) × 회전수&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;연삭기의 원주속도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;원주길이가 이미 주어졌으니 πD를 다시 구할 것이 없다&lt;/strong&gt; — &lt;strong&gt;mm를 m로 바꾸는 것&lt;/strong&gt;만 잊지 않으면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;원주속도 = 원주길이(m) × 회전수&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7528,7 +7528,7 @@
       </c>
       <c r="AI50" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지게차의 헤드가드&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;0.903 과 1.88 이라는 어중간한 값&lt;/strong&gt;이 헤드가드 기준의 특징이다 — &lt;strong&gt;1.5 나 1.8 처럼 반듯한 수로 바꿔 놓으면 틀린 보기&lt;/strong&gt;다. &lt;strong&gt;강도 한도는 4톤&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;개구 16cm 미만, 앉아서 0.903m, 서서 1.88m, 4톤&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 현행 안전보건규칙 제180조도 개구 16cm 미만, 등분포정하중 한도 4톤, 앉은 자세 0.903m 이상, 선 자세 1.88m 이상을 그대로 두고 있다. 문항에 붙은 개정 안내는 다른 조항에 관한 것이다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;지게차의 헤드가드&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;0.903과 1.88이라는 어중간한 값&lt;/strong&gt;이 헤드가드 기준의 특징이다 — &lt;strong&gt;1.5 나 1.8 처럼 반듯한 수로 바꿔 놓으면 틀린 보기&lt;/strong&gt;다. &lt;strong&gt;강도 한도는 4톤&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;개구 16cm 미만, 앉아서 0.903m, 서서 1.88m, 4톤&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 현행 안전보건규칙 제180조도 개구 16cm 미만, 등분포정하중 한도 4톤, 앉은 자세 0.903m 이상, 선 자세 1.88m 이상을 그대로 두고 있다. 문항에 붙은 개정 안내는 다른 조항에 관한 것이다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8039,12 +8039,12 @@
       </c>
       <c r="AH54" s="32" t="inlineStr">
         <is>
-          <t>① 다리는 180mm 다.&lt;br&gt;② 발은 120mm 다.&lt;br&gt;③ 손목은 100mm 다.</t>
+          <t>① 다리는 180mm다.&lt;br&gt;② 발은 120mm다.&lt;br&gt;③ 손목은 100mm다.</t>
         </is>
       </c>
       <c r="AI54" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;공간함정과 최소 틈새&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;몸이 클수록 큰 틈이 필요&lt;/strong&gt; 하다 — &lt;strong&gt;몸 500 · 다리 180 · 발과 팔 120 · 손목 100 · 손가락 25&lt;/strong&gt;로 내려간다. &lt;strong&gt;가장 작은 손가락 25mm 는 외우기 쉬워 정답이 되기 쉽다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;손가락 25mm, 손목 100mm, 발 120mm, 다리 180mm&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;공간함정과 최소 틈새&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;몸이 클수록 큰 틈이 필요&lt;/strong&gt;하다 — &lt;strong&gt;몸 500 · 다리 180 · 발과 팔 120 · 손목 100 · 손가락 25&lt;/strong&gt;로 내려간다. &lt;strong&gt;가장 작은 손가락 25mm는 외우기 쉬워 정답이 되기 쉽다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;손가락 25mm, 손목 100mm, 발 120mm, 다리 180mm&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8550,7 +8550,7 @@
       </c>
       <c r="AG58" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;시간기준보전(TBM)&lt;/strong&gt;이다. &lt;strong&gt;정해진 기간마다&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;설비보전의 갈래&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보전&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;언제&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시간기준보전(TBM)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정해진 기간마다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · 정기보전&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상태기준보전(CBM)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설비의 상태를 재어 필요할 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;예지보전&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사후보전(BM)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고장이 난 뒤에&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;개량보전(CM)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설비 자체를 고쳐 고장이 덜 나게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보전예방(MP)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계 단계부터 보전이 쉽게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;시간기준보전(TBM)&lt;/strong&gt;이다. &lt;strong&gt;정해진 기간마다&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;설비보전의 갈래&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보전&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;언제&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시간기준보전(TBM)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정해진 기간마다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · 정기보전&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상태기준보전(CBM)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설비의 상태를 재어 필요할 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;예지보전&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사후보전(BM)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고장이 난 뒤에&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;개량보전(CM)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설비 자체를 고쳐 고장이 덜 나게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보전예방(MP)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설계 단계부터 보전이 쉽게&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH58" s="32" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="AG59" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;(15 + 1.1V)% 이내&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차의 안정도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안정도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 시 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4% 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5톤 이상은 3.5% 이내&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 시 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;18% 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 시 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6% 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 시 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;(15 + 1.1V)% 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · V 는 km/h&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;(15 + 1.1V)% 이내&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차의 안정도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;상태&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안정도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 시 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4% 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;5톤 이상은 3.5% 이내&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 시 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;18% 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 시 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6% 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 시 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;(15 + 1.1V)% 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · V는 km/h&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH59" s="32" t="inlineStr">
         <is>
-          <t>② (15+1.5V)% 는 계수가 다르다.&lt;br&gt;③ (20+1.1V)% 는 상수가 다르다.&lt;br&gt;④ (20+1.5V)% 는 둘 다 다르다.</t>
+          <t>② (15+1.5V)%는 계수가 다르다.&lt;br&gt;③ (20+1.1V)%는 상수가 다르다.&lt;br&gt;④ (20+1.5V)%는 둘 다 다르다.</t>
         </is>
       </c>
       <c r="AI59" s="32" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="AI61" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;금형의 설치·해체&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;볼트가 깊이 물려야 빠지지 않는다&lt;/strong&gt; — &lt;strong&gt;「지름 이하」로 얕게 물리면 금형이 떨어진다&lt;/strong&gt;. &lt;strong&gt;안전 기준에서 「이하 · 짧게」가 나오면 한 번 더 의심&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;T홈 안길이는 볼트 지름의 2배 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;금형의 설치·해체&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;볼트가 깊이 물려야 빠지지 않는다&lt;/strong&gt; — &lt;strong&gt;「지름 이하」로 얕게 물리면 금형이 떨어진다&lt;/strong&gt;. &lt;strong&gt;안전 기준에서 「이하 · 짧게」가 나오면 한 번 더 의심&lt;/strong&gt;한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;T홈 안길이는 볼트 지름의 2배 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="U65" s="32" t="inlineStr">
         <is>
-          <t>인체의 저항을 500[Ω]으로 볼 때 심실세동을 일으키는 전류에서의 전기에너지는 약 몇 [J]인가? (단, 심실세동전류는 165/√T [mA] 이며, 통전시간 T는 1초, 전원은 정현파 교류이다.)</t>
+          <t>인체의 저항을 500[Ω]으로 볼 때 심실세동을 일으키는 전류에서의 전기에너지는 약 몇 [J]인가? (단, 심실세동전류는 165/√T [mA]이며, 통전시간 T는 1초, 전원은 정현파 교류이다.)</t>
         </is>
       </c>
       <c r="V65" s="32" t="inlineStr"/>
@@ -9458,12 +9458,12 @@
       </c>
       <c r="AH65" s="32" t="inlineStr">
         <is>
-          <t>① 3.3 은 계산과 맞지 않는다.&lt;br&gt;② 13.0 은 어림이 지나치다.&lt;br&gt;④ 272.2 는 전류를 mA 그대로 넣은 값이다.</t>
+          <t>① 3.3은 계산과 맞지 않는다.&lt;br&gt;② 13.0은 어림이 지나치다.&lt;br&gt;④ 272.2는 전류를 mA 그대로 넣은 값이다.</t>
         </is>
       </c>
       <c r="AI65" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;위험한계에너지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;mA 를 A 로 고치는 것&lt;/strong&gt;이 유일한 함정이다 — &lt;strong&gt;165mA = 0.165A&lt;/strong&gt;다. &lt;strong&gt;「13.6 J」이라는 값은 통째로 외워 두면 검산에 쓸 수 있다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;500Ω · 1초의 위험한계에너지는 13.6 J&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;위험한계에너지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;mA를 A로 고치는 것&lt;/strong&gt;이 유일한 함정이다 — &lt;strong&gt;165mA = 0.165A&lt;/strong&gt;다. &lt;strong&gt;「13.6 J」이라는 값은 통째로 외워 두면 검산에 쓸 수 있다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;500Ω · 1초의 위험한계에너지는 13.6 J&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9587,12 +9587,12 @@
       </c>
       <c r="AH66" s="32" t="inlineStr">
         <is>
-          <t>① 5 J 은 계산과 맞지 않는다.&lt;br&gt;② 30 J 도 그렇다.&lt;br&gt;④ 825 J 는 전류를 잘못 넣은 값이다.</t>
+          <t>① 5 J은 계산과 맞지 않는다.&lt;br&gt;② 30 J 도 그렇다.&lt;br&gt;④ 825 J는 전류를 잘못 넣은 값이다.</t>
         </is>
       </c>
       <c r="AI66" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;위험한계에너지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;500Ω 일 때 13.6 J&lt;/strong&gt;을 외워 두면 &lt;strong&gt;5,000Ω 은 그 10배인 136 J&lt;/strong&gt;로 곧장 나온다 — &lt;strong&gt;저항만 바꿔 되풀이 출제&lt;/strong&gt; 되는 문항이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;5,000Ω 이면 136 J&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;위험한계에너지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;500Ω 일 때 13.6 J&lt;/strong&gt;을 외워 두면 &lt;strong&gt;5,000Ω 은 그 10배인 136 J&lt;/strong&gt;로 곧장 나온다 — &lt;strong&gt;저항만 바꿔 되풀이 출제&lt;/strong&gt;되는 문항이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;5,000Ω 이면 136 J&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="AH68" s="32" t="inlineStr">
         <is>
-          <t>② 6m 이상은 35kV 를 넘을 때다.&lt;br&gt;③ 7m 이상은 기준값이 아니다.&lt;br&gt;④ 9m 이상도 그렇다.</t>
+          <t>② 6m 이상은 35kV를 넘을 때다.&lt;br&gt;③ 7m 이상은 기준값이 아니다.&lt;br&gt;④ 9m 이상도 그렇다.</t>
         </is>
       </c>
       <c r="AI68" s="32" t="inlineStr">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="AI69" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방폭기기의 그룹&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;더 엄격한 기기를 덜 엄격한 곳에 쓰는 것은 되고, 그 반대는 안 된다&lt;/strong&gt; — &lt;strong&gt;ⅡC 가 가장 엄격&lt;/strong&gt; 하다는 방향만 잡으면 ④가 뒤집혔음이 보인다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;ⅡC 기기는 ⅡA·ⅡB 지역에도 쓸 수 있다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방폭기기의 그룹&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;더 엄격한 기기를 덜 엄격한 곳에 쓰는 것은 되고, 그 반대는 안 된다&lt;/strong&gt; — &lt;strong&gt;ⅡC가 가장 엄격&lt;/strong&gt; 하다는 방향만 잡으면 ④가 뒤집혔음이 보인다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;ⅡC 기기는 ⅡA·ⅡB 지역에도 쓸 수 있다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10211,7 +10211,7 @@
       </c>
       <c r="AG71" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;2중 안전 보장으로 0종 장소에 쓸 수 있는 것은 ia&lt;/strong&gt;다. &lt;strong&gt;ib 는 1중 보장으로 1종·2종&lt;/strong&gt; 에만 쓴다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;본질안전 방폭구조의 등급&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안전 보장&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용 장소&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Exia&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2중 고장에도 안전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0종 · 1종 · 2종&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Exib&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1중 고장에 안전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1종 · 2종&lt;/u&gt; · 「0종」이 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Exic&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정상 상태에서 안전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2종&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0종 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;위험분위기가 늘 있는 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;본질안전(ia)만 쓸 수 있다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;2중 안전 보장으로 0종 장소에 쓸 수 있는 것은 ia&lt;/strong&gt;다. &lt;strong&gt;ib는 1중 보장으로 1종·2종&lt;/strong&gt; 에만 쓴다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;본질안전 방폭구조의 등급&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;안전 보장&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사용 장소&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Exia&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2중 고장에도 안전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0종 · 1종 · 2종&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Exib&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1중 고장에 안전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1종 · 2종&lt;/u&gt; · 「0종」이 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Exic&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정상 상태에서 안전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2종&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0종 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;위험분위기가 늘 있는 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;본질안전(ia)만 쓸 수 있다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH71" s="32" t="inlineStr">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="AI71" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;본질안전 방폭구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「ia 는 0종까지, ib 는 1종부터」&lt;/strong&gt;가 갈림선이다 — &lt;strong&gt;0종 장소에 쓸 수 있는 것은 오직 ia&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0종에 쓸 수 있는 것은 ia 뿐&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;본질안전 방폭구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「ia는 0종까지, ib는 1종부터」&lt;/strong&gt;가 갈림선이다 — &lt;strong&gt;0종 장소에 쓸 수 있는 것은 오직 ia&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;0종에 쓸 수 있는 것은 ia뿐&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10737,7 +10737,7 @@
       </c>
       <c r="AI75" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정상 상태의 점화원&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;물음이 「정상적으로 회전 중에」&lt;/strong&gt; 라고 못 박았다 — &lt;strong&gt;보기 셋은 모두 접점이 여닫힐 때만&lt;/strong&gt; 불꽃이 나고 &lt;strong&gt;회전하는 것은 슬립링 하나&lt;/strong&gt; 뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;회전 중에도 불꽃이 나는 것은 슬립링&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정상 상태의 점화원&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;물음이 「정상적으로 회전 중에」&lt;/strong&gt; 라고 못 박았다 — &lt;strong&gt;보기 셋은 모두 접점이 여닫힐 때만&lt;/strong&gt; 불꽃이 나고 &lt;strong&gt;회전하는 것은 슬립링 하나&lt;/strong&gt;뿐이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;회전 중에도 불꽃이 나는 것은 슬립링&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="AH81" s="32" t="inlineStr">
         <is>
-          <t>① 20% 는 계산과 맞지 않는다.&lt;br&gt;③ 45% 도 그렇다.&lt;br&gt;④ 50% 는 반감기의 개념이다.</t>
+          <t>① 20%는 계산과 맞지 않는다.&lt;br&gt;③ 45% 도 그렇다.&lt;br&gt;④ 50%는 반감기의 개념이다.</t>
         </is>
       </c>
       <c r="AI81" s="32" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="AI84" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지하작업장의 가스 측정&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;하루 일과를 오전·오후로 나누면 4시간&lt;/strong&gt;이다 — &lt;strong&gt;6시간이면 반나절을 그냥 지나친다&lt;/strong&gt;. &lt;strong&gt;25% 라는 대피 기준과 함께&lt;/strong&gt; 묶어 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;장시간 작업은 4시간마다 측정&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;지하작업장의 가스 측정&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;하루 일과를 오전·오후로 나누면 4시간&lt;/strong&gt;이다 — &lt;strong&gt;6시간이면 반나절을 그냥 지나친다&lt;/strong&gt;. &lt;strong&gt;25%라는 대피 기준과 함께&lt;/strong&gt; 묶어 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;장시간 작업은 4시간마다 측정&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12014,7 +12014,7 @@
       </c>
       <c r="AH85" s="32" t="inlineStr">
         <is>
-          <t>② |L−U|/U 는 상한계로 나눈 꼴이다.&lt;br&gt;③ L/(U−L) 은 분자와 분모를 뒤바꾼 꼴이다.&lt;br&gt;④ U/|L−U| 도 그렇다.</t>
+          <t>② |L−U|/U는 상한계로 나눈 꼴이다.&lt;br&gt;③ L/(U−L)은 분자와 분모를 뒤바꾼 꼴이다.&lt;br&gt;④ U/|L−U| 도 그렇다.</t>
         </is>
       </c>
       <c r="AI85" s="32" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="AH86" s="32" t="inlineStr">
         <is>
-          <t>① 1 kPa 은 거의 진공에 가깝다.&lt;br&gt;② 100 kPa 은 반올림한 값이라 기준값이 아니다.&lt;br&gt;④ 273.15 는 온도 환산에 쓰는 수다.</t>
+          <t>① 1 kPa은 거의 진공에 가깝다.&lt;br&gt;② 100 kPa은 반올림한 값이라 기준값이 아니다.&lt;br&gt;④ 273.15는 온도 환산에 쓰는 수다.</t>
         </is>
       </c>
       <c r="AI86" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;인화성 액체의 정의&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1기압 = 101.3 kPa = 760 mmHg&lt;/strong&gt;다 — &lt;strong&gt;273.15 는 온도, 101.3 은 압력&lt;/strong&gt;이라는 것만 가르면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;표준압력은 101.3 kPa&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;인화성 액체의 정의&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1기압 = 101.3 kPa = 760 mmHg&lt;/strong&gt;다 — &lt;strong&gt;273.15는 온도, 101.3은 압력&lt;/strong&gt;이라는 것만 가르면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;표준압력은 101.3 kPa&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12272,7 +12272,7 @@
       </c>
       <c r="AH87" s="32" t="inlineStr">
         <is>
-          <t>① 5m 는 기준값이 아니다.&lt;br&gt;③ 15m 도 그렇다.&lt;br&gt;④ 20m 는 나머지 세 경우의 기준이다.</t>
+          <t>① 5m는 기준값이 아니다.&lt;br&gt;③ 15m 도 그렇다.&lt;br&gt;④ 20m는 나머지 세 경우의 기준이다.</t>
         </is>
       </c>
       <c r="AI87" s="32" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="AI88" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;급성 독성물질의 기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「경구 300 · 경피 1,000 · 가스 2,500」&lt;/strong&gt; 세 수다 — &lt;strong&gt;경피는 토끼와 쥐가 같은 값&lt;/strong&gt;이라 동물만 바꿔 놓고 수를 두 배로 늘린 보기가 틀렸다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;경피 LD50 은 1,000mg/kg 이하&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;급성 독성물질의 기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「경구 300 · 경피 1,000 · 가스 2,500」&lt;/strong&gt; 세 수다 — &lt;strong&gt;경피는 토끼와 쥐가 같은 값&lt;/strong&gt;이라 동물만 바꿔 놓고 수를 두 배로 늘린 보기가 틀렸다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;경피 LD50은 1,000mg/kg 이하&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12525,17 +12525,17 @@
       </c>
       <c r="AG89" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;2,500 ppm 이하&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;LD50 과 LC50&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;LD50&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;실험동물의 절반을 죽이는 투여량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;mg/kg · 경구·경피&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;LC50&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;실험동물의 절반을 죽이는 공기 중 농도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;ppm 또는 mg/L · 흡입&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가스 LC50&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2,500 ppm 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50 의 뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Lethal(치사) 50%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;2,500 ppm 이하&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;LD50과 LC50&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;LD50&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;실험동물의 절반을 죽이는 투여량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;mg/kg · 경구·경피&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;LC50&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;실험동물의 절반을 죽이는 공기 중 농도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;ppm 또는 mg/L · 흡입&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가스 LC50&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2,500 ppm 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;50의 뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Lethal(치사) 50%&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH89" s="32" t="inlineStr">
         <is>
-          <t>① 1,500ppm 은 기준값이 아니다.&lt;br&gt;③ 3,000ppm 도 그렇다.&lt;br&gt;④ 4,000ppm 도 그렇다.</t>
+          <t>① 1,500ppm은 기준값이 아니다.&lt;br&gt;③ 3,000ppm 도 그렇다.&lt;br&gt;④ 4,000ppm 도 그렇다.</t>
         </is>
       </c>
       <c r="AI89" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;LC50&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「L」은 Lethal(치사), 「D」는 Dose(용량), 「C」는 Concentration(농도)&lt;/strong&gt;다 — &lt;strong&gt;먹거나 바르면 D, 마시면 C&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가스 LC50 은 2,500ppm 이하&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;LC50&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「L」은 Lethal(치사), 「D」는 Dose(용량), 「C」는 Concentration(농도)&lt;/strong&gt;다 — &lt;strong&gt;먹거나 바르면 D, 마시면 C&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가스 LC50은 2,500ppm 이하&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="AH91" s="32" t="inlineStr">
         <is>
-          <t>② 통기밸브는 저장탱크의 압력을 대기와 맞추는 장치다.&lt;br&gt;③ 체크밸브는 역류를 막는 밸브다.&lt;br&gt;④ Flame arrester 는 화염의 전파를 막는 장치다.</t>
+          <t>② 통기밸브는 저장탱크의 압력을 대기와 맞추는 장치다.&lt;br&gt;③ 체크밸브는 역류를 막는 밸브다.&lt;br&gt;④ Flame arrester는 화염의 전파를 막는 장치다.</t>
         </is>
       </c>
       <c r="AI91" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;파열판&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;안전밸브는 「열고 닫는」 것이라 반응이 느리다&lt;/strong&gt; — &lt;strong&gt;한순간에 치솟는 압력에는 아예 찢어지는 파열판&lt;/strong&gt; 이라야 따라간다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;급격한 압력상승에는 파열판&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;파열판&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;안전밸브는 「열고 닫는」 것이라 반응이 느리다&lt;/strong&gt; — &lt;strong&gt;한순간에 치솟는 압력에는 아예 찢어지는 파열판&lt;/strong&gt;이라야 따라간다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;급격한 압력상승에는 파열판&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13170,17 +13170,17 @@
       </c>
       <c r="AG94" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;BLEVE(비등액 팽창증기 폭발)&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;BLEVE 와 UVCE&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;BLEVE&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;끓는점 아래에 있던 액체가 가열되어 용기가 터지며 한꺼번에 증발·팽창&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · 뒤이어 파이어볼&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;UVCE&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;새어 나온 가연성 증기가 대기 중에 구름을 이루고 발화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;증기운 폭발&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;막는 법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;탱크에 물을 뿌려 식힌다 · 단열 · 방액제 · 압력방출&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;BLEVE(비등액 팽창증기 폭발)&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;BLEVE와 UVCE&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;BLEVE&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;끓는점 아래에 있던 액체가 가열되어 용기가 터지며 한꺼번에 증발·팽창&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · 뒤이어 파이어볼&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;UVCE&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;새어 나온 가연성 증기가 대기 중에 구름을 이루고 발화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;증기운 폭발&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;막는 법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;탱크에 물을 뿌려 식힌다 · 단열 · 방액제 · 압력방출&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH94" s="32" t="inlineStr">
         <is>
-          <t>② UVCE 는 대기 중 증기운 폭발이다.&lt;br&gt;③ 개방계 폭발은 갈래 이름일 뿐 이 현상의 이름이 아니다.&lt;br&gt;④ 밀폐계 폭발도 그렇다.</t>
+          <t>② UVCE는 대기 중 증기운 폭발이다.&lt;br&gt;③ 개방계 폭발은 갈래 이름일 뿐 이 현상의 이름이 아니다.&lt;br&gt;④ 밀폐계 폭발도 그렇다.</t>
         </is>
       </c>
       <c r="AI94" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;BLEVE&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;BLEVE 는 Boiling Liquid Expanding Vapor Explosion&lt;/strong&gt;의 머리글자다 — &lt;strong&gt;「끓는 액체가 부풀어 오르는 증기 폭발」&lt;/strong&gt;이라는 이름 그대로다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;용기가 가열돼 터지며 증발하면 BLEVE&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;BLEVE&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;BLEVE는 Boiling Liquid Expanding Vapor Explosion&lt;/strong&gt;의 머리글자다 — &lt;strong&gt;「끓는 액체가 부풀어 오르는 증기 폭발」&lt;/strong&gt;이라는 이름 그대로다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;용기가 가열돼 터지며 증발하면 BLEVE&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="AI96" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;혼촉발화&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「산화제 + 가연물」이 만나면 위험&lt;/strong&gt; 하다 — &lt;strong&gt;발연질산은 대표적인 강산화제, 아닐린은 가연성 유기물&lt;/strong&gt;이다. &lt;strong&gt;나머지 셋은 성질이 비슷하거나 서로 무관한 짝&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;발연질산 + 아닐린은 혼촉발화&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;혼촉발화&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「산화제 + 가연물」이 만나면 위험&lt;/strong&gt;하다 — &lt;strong&gt;발연질산은 대표적인 강산화제, 아닐린은 가연성 유기물&lt;/strong&gt;이다. &lt;strong&gt;나머지 셋은 성질이 비슷하거나 서로 무관한 짝&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;발연질산 + 아닐린은 혼촉발화&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13940,7 +13940,7 @@
       </c>
       <c r="AG100" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;소요동력은 회전수의 세제곱에 비례&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;송풍기의 상사법칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;회전수와의 관계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Q_{2} = Q_{1} \times ( N_{2} / N_{1} )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1승에 비례&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P_{2} = P_{1} \times ( N_{2} / N_{1} )^{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제곱에 비례&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;소요동력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$L_{2} = L_{1} \times ( N_{2} / N_{1} )^{3}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;세제곱에 비례&lt;/u&gt; · ③&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;외우는 법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「양 1 · 압 2 · 력 3」&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;소요동력은 회전수의 세제곱에 비례&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;송풍기의 상사법칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;회전수와의 관계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Q_{2} = Q_{1} \times ( N_{2} / N_{1} )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1승에 비례&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P_{2} = P_{1} \times ( N_{2} / N_{1} )^{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제곱에 비례&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;소요동력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$L_{2} = L_{1} \times ( N_{2} / N_{1} )^{3}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;세제곱에 비례&lt;/u&gt; · ③&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;외우는 법&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「양 1 · 압 2 · 력 3」&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH100" s="32" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="AI102" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;제4류 위험물의 구분&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「휘발유 1 · 등유 2 · 중유 3 · 실린더유 4」&lt;/strong&gt;로 번호가 그대로 붙는다 — &lt;strong&gt;네 보기가 1 · 2 · 3 · 4 에 하나씩&lt;/strong&gt; 놓여 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;등유·경유가 제2석유류&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;제4류 위험물의 구분&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「휘발유 1 · 등유 2 · 중유 3 · 실린더유 4」&lt;/strong&gt;로 번호가 그대로 붙는다 — &lt;strong&gt;네 보기가 1 · 2 · 3 · 4에 하나씩&lt;/strong&gt; 놓여 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;등유·경유가 제2석유류&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14332,7 +14332,7 @@
       </c>
       <c r="AH103" s="32" t="inlineStr">
         <is>
-          <t>② 2.5m 는 기준값이 아니다.&lt;br&gt;③ 3.5m 도 그렇다.&lt;br&gt;④ 4.5m 도 그렇다.</t>
+          <t>② 2.5m는 기준값이 아니다.&lt;br&gt;③ 3.5m 도 그렇다.&lt;br&gt;④ 4.5m 도 그렇다.</t>
         </is>
       </c>
       <c r="AI103" s="32" t="inlineStr">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="AG109" s="32" t="inlineStr">
         <is>
-          <t>안전난간은 &lt;strong&gt;상부난간대 · 중간난간대 · 발끝막이판 · 난간기둥&lt;/strong&gt; 넷이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전난간의 구성과 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구성&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상부난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥면에서 90cm 이상 120cm 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;120cm 를 넘으면 중간난간대를 60cm 이내마다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중간난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상부난간대와 바닥면의 중간에&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발끝막이판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥면에서 10cm 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물체가 떨어지지 않게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간기둥&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;난간대를 지탱한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;임의의 점에 100kg 이상의 하중을 견딜 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사다리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전난간의 구성요소가 아니다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>안전난간은 &lt;strong&gt;상부난간대 · 중간난간대 · 발끝막이판 · 난간기둥&lt;/strong&gt; 넷이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전난간의 구성과 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구성&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상부난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥면에서 90cm 이상 120cm 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;120cm를 넘으면 중간난간대를 60cm 이내마다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중간난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상부난간대와 바닥면의 중간에&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발끝막이판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥면에서 10cm 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물체가 떨어지지 않게&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간기둥&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;난간대를 지탱한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;임의의 점에 100kg 이상의 하중을 견딜 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사다리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전난간의 구성요소가 아니다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH109" s="32" t="inlineStr">
@@ -15239,7 +15239,7 @@
       </c>
       <c r="AH110" s="32" t="inlineStr">
         <is>
-          <t>① 30cm 는 기준값이 아니다.&lt;br&gt;③ 50cm 도 그렇다.&lt;br&gt;④ 60cm 도 그렇다.</t>
+          <t>① 30cm는 기준값이 아니다.&lt;br&gt;③ 50cm 도 그렇다.&lt;br&gt;④ 60cm 도 그렇다.</t>
         </is>
       </c>
       <c r="AI110" s="32" t="inlineStr">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="AH111" s="32" t="inlineStr">
         <is>
-          <t>① 20cm 는 기준값이 아니다.&lt;br&gt;③ 40cm 도 그렇다.&lt;br&gt;④ 50cm 도 그렇다.</t>
+          <t>① 20cm는 기준값이 아니다.&lt;br&gt;③ 40cm 도 그렇다.&lt;br&gt;④ 50cm 도 그렇다.</t>
         </is>
       </c>
       <c r="AI111" s="32" t="inlineStr">
@@ -15501,7 +15501,7 @@
       </c>
       <c r="AH112" s="32" t="inlineStr">
         <is>
-          <t>① 풍속 기준은 10분간 평균 초당 10m 이상이다.&lt;br&gt;② 강우 기준은 시간당 1mm 이상이다.&lt;br&gt;④ 10분간 평균풍속 초당 5m 는 기준값이 아니다.</t>
+          <t>① 풍속 기준은 10분간 평균 초당 10m 이상이다.&lt;br&gt;② 강우 기준은 시간당 1mm 이상이다.&lt;br&gt;④ 10분간 평균풍속 초당 5m는 기준값이 아니다.</t>
         </is>
       </c>
       <c r="AI112" s="32" t="inlineStr">
@@ -15627,7 +15627,7 @@
       </c>
       <c r="AI113" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전관리의 순환&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「세우고 → 하고 → 살피고 → 고친다」&lt;/strong&gt;는 데밍의 순환이다 — &lt;strong&gt;살펴본 뒤라야 고칠 것을 안다&lt;/strong&gt;는 점에서 C 가 A 보다 앞선다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;Plan · Do · Check · Action&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전관리의 순환&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「세우고 → 하고 → 살피고 → 고친다」&lt;/strong&gt;는 데밍의 순환이다 — &lt;strong&gt;살펴본 뒤라야 고칠 것을 안다&lt;/strong&gt;는 점에서 C가 A보다 앞선다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;Plan · Do · Check · Action&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15746,7 +15746,7 @@
       </c>
       <c r="AG114" s="32" t="inlineStr">
         <is>
-          <t>달줄·달포대는 &lt;strong&gt;쓰도록 해야&lt;/strong&gt; 한다. &lt;strong&gt;던져 올리고 내리면 위험&lt;/strong&gt; 하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;거푸집동바리 조립·해체 시 준수사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관계 근로자가 아닌 사람의 출입을 금지한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비·눈 등으로 날씨가 몹시 나쁘면 작업을 중지한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;재료·기구·공구를 올리거나 내릴 때는 달줄·달포대를 쓰게 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「금하도록」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버팀목을 설치하고 인양장비에 매단 뒤 작업한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;낙하·충격 방지&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>달줄·달포대는 &lt;strong&gt;쓰도록 해야&lt;/strong&gt; 한다. &lt;strong&gt;던져 올리고 내리면 위험&lt;/strong&gt;하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;거푸집동바리 조립·해체 시 준수사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;관계 근로자가 아닌 사람의 출입을 금지한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비·눈 등으로 날씨가 몹시 나쁘면 작업을 중지한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;재료·기구·공구를 올리거나 내릴 때는 달줄·달포대를 쓰게 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「금하도록」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;버팀목을 설치하고 인양장비에 매단 뒤 작업한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;낙하·충격 방지&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH114" s="32" t="inlineStr">
@@ -15885,7 +15885,7 @@
       </c>
       <c r="AI115" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;크레인 사용 시 준수사항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;크레인은 「곧게 위로만 들어 올리는」 기계&lt;/strong&gt;다 — &lt;strong&gt;옆으로 끌면 로프에 옆힘이 걸려 위험&lt;/strong&gt; 하다. &lt;strong&gt;보기 셋이 「하지 아니할 것」이고 하나만 「할 것」&lt;/strong&gt;이라 눈에 띈다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;끌어당기거나 밀어내는 작업은 금지&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;크레인 사용 시 준수사항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;크레인은 「곧게 위로만 들어 올리는」 기계&lt;/strong&gt;다 — &lt;strong&gt;옆으로 끌면 로프에 옆힘이 걸려 위험&lt;/strong&gt;하다. &lt;strong&gt;보기 셋이 「하지 아니할 것」이고 하나만 「할 것」&lt;/strong&gt;이라 눈에 띈다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;끌어당기거나 밀어내는 작업은 금지&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16778,7 +16778,7 @@
       </c>
       <c r="AG122" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;난간을 딛거나 받침대·사다리를 놓고 작업해서는 안 된다&lt;/strong&gt;. &lt;strong&gt;발판 위에 또 무엇을 올려 서면 넘어진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;이동식 비계의 준수사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;바퀴에 구름방지장치를 하고 아웃트리거를 설치한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;승강용 사다리를 견고하게 설치한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최상부에서 작업할 때는 안전난간을 설치한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업발판의 최대적재하중은 250kg 을 넘지 않게 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업발판 위에서 안전난간을 딛거나 받침대·사다리를 쓰지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④가 틀린 까닭&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 중 이동식 비계를 옮기지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;난간을 딛거나 받침대·사다리를 놓고 작업해서는 안 된다&lt;/strong&gt;. &lt;strong&gt;발판 위에 또 무엇을 올려 서면 넘어진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;이동식 비계의 준수사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;바퀴에 구름방지장치를 하고 아웃트리거를 설치한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;승강용 사다리를 견고하게 설치한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최상부에서 작업할 때는 안전난간을 설치한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업발판의 최대적재하중은 250kg을 넘지 않게 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업발판 위에서 안전난간을 딛거나 받침대·사다리를 쓰지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④가 틀린 까닭&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업 중 이동식 비계를 옮기지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH122" s="32" t="inlineStr">
